--- a/GUESTS.xlsx
+++ b/GUESTS.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="43">
   <si>
     <t>NO</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>Dr. Ketul Oza</t>
+  </si>
+  <si>
+    <t>Dr Rajesh Patel</t>
+  </si>
+  <si>
+    <t>GUEST</t>
   </si>
 </sst>
 </file>
@@ -227,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -248,6 +254,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.5703125" customWidth="1"/>
@@ -973,6 +987,23 @@
         <v>9099026892</v>
       </c>
     </row>
+    <row r="28" spans="1:5" ht="15.75">
+      <c r="A28" s="10">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="13">
+        <v>9825291668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
